--- a/project_clean_data.xlsx
+++ b/project_clean_data.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Lower-Middle-Income, Mild-Climate</t>
+          <t>Very High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Lower-Middle-Income, Mild-Climate</t>
+          <t>Very High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Lower-Middle-Income, Mild-Climate</t>
+          <t>Very High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Lower-Middle-Income, Mild-Climate</t>
+          <t>Very High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Lower-Middle-Income, Mild-Climate</t>
+          <t>Very High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>High-Income, Moderate/Warm-Climate</t>
+          <t>High Income, Cold</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Lowest-Income, Hot-Climate</t>
+          <t>High Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Low-Income, Cold-Climate</t>
+          <t>Middle Income, Temperate</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Low-Income, Moderate-Climate</t>
+          <t>Low Income, Hot</t>
         </is>
       </c>
     </row>
